--- a/healthcare_forms/007_mental_health_outcome_measure_questionnaire--healthcare_forms.xlsx
+++ b/healthcare_forms/007_mental_health_outcome_measure_questionnaire--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -998,7 +998,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Follow up Time</t>
+          <t>Mental Health Follow Up Time</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mental_health_status_comments</t>
+          <t>mental_health_status_comments_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mental Health Status Comments</t>
+          <t>Mental Health Status Comments 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mental_health_counseling_session</t>
+          <t>mental_health_counseling_session_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mental Health Counseling Session</t>
+          <t>Mental Health Counseling Session 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1137,9 +1137,9 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'scale_1'}</t>
+          <t>scale_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Scale 1'}</t>
+          <t>Scale 1</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'scale_2'}</t>
+          <t>scale_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Scale 2'}</t>
+          <t>Scale 2</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'scale_3'}</t>
+          <t>scale_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Scale 3'}</t>
+          <t>Scale 3</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'scale_4'}</t>
+          <t>scale_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Scale 4'}</t>
+          <t>Scale 4</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'scale_5'}</t>
+          <t>scale_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Scale 5'}</t>
+          <t>Scale 5</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mental_health_counseling_session_choices</t>
+          <t>mental_health_counseling_session_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1757,7 +1757,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mental_health_counseling_session_choices</t>
+          <t>mental_health_counseling_session_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
